--- a/Modelo/datos/Intermedias/precedence_completa.xlsx
+++ b/Modelo/datos/Intermedias/precedence_completa.xlsx
@@ -1,21 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Intermedias/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_9276A7FC487FB4D266075C52F3322235616BBC4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5CFAC2D-1257-40B6-AA4F-B59BBF1D807C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="precedence" sheetId="1" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId1"/>
+    <sheet name="precedence" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precedence tiene las precedencias en pares de la matriz A completa </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +98,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +150,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +184,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +219,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,23 +395,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FD8DA5-EF91-44BA-8743-719C8B4B3223}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -374,7 +430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -382,7 +438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>15</v>
       </c>
@@ -390,7 +446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2</v>
       </c>
@@ -398,7 +454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>15</v>
       </c>
@@ -406,7 +462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>3</v>
       </c>
@@ -414,7 +470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3</v>
       </c>
@@ -422,7 +478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>4</v>
       </c>
@@ -430,7 +486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>15</v>
       </c>
@@ -438,7 +494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>30</v>
       </c>
@@ -446,7 +502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>5</v>
       </c>
@@ -454,7 +510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>6</v>
       </c>
@@ -462,7 +518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>3</v>
       </c>
@@ -470,7 +526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>4</v>
       </c>
@@ -478,7 +534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>6</v>
       </c>
@@ -486,7 +542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>7</v>
       </c>
@@ -494,7 +550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>30</v>
       </c>
@@ -502,7 +558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>3</v>
       </c>
@@ -510,7 +566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>4</v>
       </c>
@@ -518,7 +574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>6</v>
       </c>
@@ -526,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>7</v>
       </c>
@@ -534,7 +590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>30</v>
       </c>
@@ -542,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>9</v>
       </c>
@@ -550,7 +606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>15</v>
       </c>
@@ -558,7 +614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>10</v>
       </c>
@@ -566,7 +622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
@@ -574,7 +630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>28</v>
       </c>
@@ -582,7 +638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>10</v>
       </c>
@@ -590,7 +646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>11</v>
       </c>
@@ -598,7 +654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>15</v>
       </c>
@@ -606,7 +662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>10</v>
       </c>
@@ -614,7 +670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>12</v>
       </c>
@@ -622,7 +678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>13</v>
       </c>
@@ -630,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
@@ -638,7 +694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2</v>
       </c>
@@ -646,7 +702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>16</v>
       </c>
@@ -654,7 +710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>17</v>
       </c>
@@ -662,7 +718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>5</v>
       </c>
@@ -670,7 +726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>15</v>
       </c>
@@ -678,7 +734,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>2</v>
       </c>
@@ -686,7 +742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>4</v>
       </c>
@@ -694,7 +750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>8</v>
       </c>
@@ -702,7 +758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>15</v>
       </c>
@@ -710,7 +766,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>16</v>
       </c>
@@ -718,7 +774,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>17</v>
       </c>
@@ -726,7 +782,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>31</v>
       </c>
@@ -734,7 +790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>4</v>
       </c>
@@ -742,7 +798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>8</v>
       </c>
@@ -750,7 +806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>16</v>
       </c>
@@ -758,7 +814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>19</v>
       </c>
@@ -766,7 +822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>30</v>
       </c>
@@ -774,7 +830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>4</v>
       </c>
@@ -782,7 +838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>8</v>
       </c>
@@ -790,7 +846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>16</v>
       </c>
@@ -798,7 +854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>19</v>
       </c>
@@ -806,7 +862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>30</v>
       </c>
@@ -814,7 +870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>4</v>
       </c>
@@ -822,7 +878,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>8</v>
       </c>
@@ -830,7 +886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>16</v>
       </c>
@@ -838,7 +894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>19</v>
       </c>
@@ -846,7 +902,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -854,7 +910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>4</v>
       </c>
@@ -862,7 +918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>8</v>
       </c>
@@ -870,7 +926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>16</v>
       </c>
@@ -878,7 +934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>19</v>
       </c>
@@ -886,7 +942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>20</v>
       </c>
@@ -894,7 +950,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>21</v>
       </c>
@@ -902,7 +958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>22</v>
       </c>
@@ -910,7 +966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>30</v>
       </c>
@@ -918,7 +974,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>2</v>
       </c>
@@ -926,7 +982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>3</v>
       </c>
@@ -934,7 +990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>15</v>
       </c>
@@ -942,7 +998,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>16</v>
       </c>
@@ -950,7 +1006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>17</v>
       </c>
@@ -958,7 +1014,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>31</v>
       </c>
@@ -966,7 +1022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>24</v>
       </c>
@@ -974,7 +1030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>15</v>
       </c>
@@ -982,7 +1038,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>19</v>
       </c>
@@ -990,7 +1046,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>24</v>
       </c>
@@ -998,7 +1054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>31</v>
       </c>
@@ -1006,7 +1062,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>26</v>
       </c>
@@ -1014,7 +1070,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>15</v>
       </c>
@@ -1022,7 +1078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>19</v>
       </c>
@@ -1030,7 +1086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>24</v>
       </c>
@@ -1038,7 +1094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>31</v>
       </c>
@@ -1046,7 +1102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>28</v>
       </c>
@@ -1054,7 +1110,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>31</v>
       </c>
@@ -1062,7 +1118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
@@ -1070,7 +1126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>15</v>
       </c>
@@ -1078,7 +1134,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>31</v>
       </c>
@@ -1086,7 +1142,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
@@ -1094,7 +1150,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>3</v>
       </c>
@@ -1102,7 +1158,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>6</v>
       </c>
@@ -1110,7 +1166,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>8</v>
       </c>
@@ -1118,7 +1174,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
@@ -1126,7 +1182,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>3</v>
       </c>
